--- a/request_forms/038_mass_intention_request_form--request_forms.xlsx
+++ b/request_forms/038_mass_intention_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,113 +515,109 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>requested_mass_intention</t>
+          <t>mass_intention_date</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>requested_mass_intention</t>
+          <t>Date of the Event</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>requested_mass_intention</t>
+          <t>mass_intention_time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>requested_mass_intention</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Mass Intention</t>
-        </is>
-      </c>
+          <t>Time of the Mass</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>requested_by</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Requested By</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>mass_intention_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Intention of the Mass</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>requested_by</t>
+          <t>mass_intention_additional_comments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>requested_by</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -639,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>requested_mass_intention</t>
+          <t>mass_location</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>requested_mass_intention</t>
+          <t>Location of the Mass</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>requested_mass_intention_1</t>
+          <t>mass_saint</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>requested_mass_intention</t>
+          <t>Saint</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>requested_mass_intention_2</t>
+          <t>mass_saint_name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>requested_mass_intention</t>
+          <t>Saint's Name</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,23 +699,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>requested_mass_intention_3</t>
+          <t>mass_for_who</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>requested_mass_intention</t>
+          <t>Mass is for</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -731,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>requested_mass_intention_4</t>
+          <t>mass_for_who_else</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>requested_mass_intention</t>
+          <t>Mass is for (if not for the requestor)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -754,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>requested_mass_intention_5</t>
+          <t>mass_liturgy_requests</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>requested_mass_intention</t>
+          <t>Liturgical Requests</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -777,108 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>requested_mass_intention_6</t>
+          <t>mass_location_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>requested_mass_intention</t>
+          <t>Mass Location</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>requested_mass_intention_7</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>requested_mass_intention</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>requested_mass_intention_8</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>requested_mass_intention</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>requested_mass_intention_9</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>requested_mass_intention</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>requested_mass_intention_10</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>requested_mass_intention</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -895,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -928,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>i_am_requesting_the_mass_for_myself</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>I am requesting the mass for myself</t>
         </is>
       </c>
     </row>
@@ -945,12 +849,165 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>i_am_requesting_the_mass_for_someone_else</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>I am requesting the mass for someone else</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mass_intention_type_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>requiem</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Requiem</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mass_intention_type_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rosary</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Rosary</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mass_intention_type_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mass_of_the_sick</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mass of the Sick</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mass_intention_type_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>mass_of_the_dead</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mass of the Dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mass_intention_type_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mass_saint_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>saint</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Saint</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mass_saint_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mass_for_who_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>me</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Me</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mass_for_who_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>someone_else_(specify_below)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Someone Else (specify below)</t>
         </is>
       </c>
     </row>
